--- a/data/trans_orig/IP19C08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39755</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46128</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35202</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>78250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86894</t>
+          <t>86442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19344</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7661</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19090</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33962</t>
+          <t>32144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210359</t>
+          <t>209794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221145</t>
+          <t>220993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>233123</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>226379</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>237627</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>92,13%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>233123</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>226633</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>238062</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440083</t>
+          <t>441901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455992</t>
+          <t>456642</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65973</t>
+          <t>65815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73533</t>
+          <t>73367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69008</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136483</t>
+          <t>137233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145384</t>
+          <t>145686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322820</t>
+          <t>322948</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336989</t>
+          <t>336962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>337109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349818</t>
+          <t>350395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662495</t>
+          <t>664613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683718</t>
+          <t>683954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>42383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85696</t>
+          <t>85315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90321</t>
+          <t>90327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28579</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202253</t>
+          <t>202798</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213674</t>
+          <t>213190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226667</t>
+          <t>226449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236117</t>
+          <t>236119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432812</t>
+          <t>433439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447585</t>
+          <t>448366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77917</t>
+          <t>78330</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84228</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75451</t>
+          <t>75651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81398</t>
+          <t>81388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156464</t>
+          <t>156575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164786</t>
+          <t>164704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>332224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344030</t>
+          <t>344843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345870</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357131</t>
+          <t>357760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682043</t>
+          <t>681765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>699455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234132</t>
+          <t>234088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245269</t>
+          <t>245251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237499</t>
+          <t>236366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247040</t>
+          <t>246561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>474101</t>
+          <t>475657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>489904</t>
+          <t>489896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83245</t>
+          <t>82734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87240</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>82955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168343</t>
+          <t>168684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174262</t>
+          <t>174269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341352</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353947</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351861</t>
+          <t>351749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361856</t>
+          <t>361866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>698205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713164</t>
+          <t>713397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51257</t>
+          <t>50965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250328</t>
+          <t>250214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>259282</t>
+          <t>258900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297978</t>
+          <t>297910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320346</t>
+          <t>320061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554098</t>
+          <t>554395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>577023</t>
+          <t>577225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>94215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99231</t>
+          <t>99202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123177</t>
+          <t>122463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>132801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219503</t>
+          <t>219803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230838</t>
+          <t>230894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377641</t>
+          <t>376728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387084</t>
+          <t>386795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>452431</t>
+          <t>451611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475364</t>
+          <t>474928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836087</t>
+          <t>836323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>859615</t>
+          <t>859824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3510</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3055</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7350</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7320</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39381</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35482</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41555</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43871</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39576</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>46136</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46231</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39381</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35571</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41539</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78250</t>
+          <t>78424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>86937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,64 +1066,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8032</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11863</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7329</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18528</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18927</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19344</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1179,67 +1179,67 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233123</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>227045</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>237691</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>216459</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>209794</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>220993</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>209395</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>220813</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>233123</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>226379</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>237627</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441901</t>
+          <t>440631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456642</t>
+          <t>456324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4751</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5117</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9868</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4231</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71754</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68366</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70566</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65815</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73367</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73510</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71754</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68886</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137233</t>
+          <t>136727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145686</t>
+          <t>145353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11614</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25056</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27982</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14335</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11336</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24622</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>344258</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>336675</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>350117</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>330895</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>322948</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>336962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>323244</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>336595</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>344258</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>337109</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>350395</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>664613</t>
+          <t>664287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683954</t>
+          <t>683784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,92 +2326,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5569</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1919</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5212</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41044</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37394</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42361</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41044</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37751</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42383</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85315</t>
+          <t>85585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90327</t>
+          <t>90317</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4774</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15088</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11431</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7288</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17680</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6740</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17531</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8958</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14464</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>231955</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>225825</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236139</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209047</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>202798</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>213190</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>202947</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>213738</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>231955</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>226449</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>236119</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433439</t>
+          <t>432768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448366</t>
+          <t>447082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7683</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3481</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7218</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2913</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6474</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79212</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74442</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81398</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82067</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78330</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84225</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77905</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84243</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79212</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75651</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81388</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156575</t>
+          <t>155669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164704</t>
+          <t>164581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20159</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21767</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8974</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22241</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20937</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>352212</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>345843</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>357269</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>339079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>332224</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>344843</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>331750</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>345017</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>352212</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>345065</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>357760</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681765</t>
+          <t>682198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699455</t>
+          <t>699123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4042,47 +4042,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8286</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4706</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12064</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7489</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18652</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7050</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19194</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8286</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4759</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14954</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>29115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>243034</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>236642</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>246614</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>353</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>240676</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>234088</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>245251</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>233546</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>245690</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>243034</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>236366</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>246561</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>475657</t>
+          <t>474944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>489896</t>
+          <t>490379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>251320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>251320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>251320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>251320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>251320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>251320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5042</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1769</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5006</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>86272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82656</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>85971</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82734</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>87243</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82877</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>87247</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86272</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82955</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168684</t>
+          <t>168422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174269</t>
+          <t>174723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16416</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21034</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8650</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20898</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>357445</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>350742</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>361395</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>348785</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>341584</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>353993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>341720</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>353968</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>357445</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>351749</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>361866</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698205</t>
+          <t>697882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713397</t>
+          <t>713767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3597</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4016</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23304</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20693</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26643</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24349</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21468</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25484</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,24%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54079</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50965</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,74 +5875,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8628</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27457</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11613</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11811</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8696</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2954</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25105</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>300917</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>282088</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>306759</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>255720</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>250214</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>258900</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>259894</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>254241</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>263550</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>95,56%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>314319</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>297910</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>320061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>570039</t>
+          <t>560811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554395</t>
+          <t>544918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>577225</t>
+          <t>568301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12019</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2561</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5861</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121344</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115241</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124233</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97515</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94215</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99202</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>129407</t>
+          <t>101118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122463</t>
+          <t>97382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>102661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>226922</t>
+          <t>222461</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219803</t>
+          <t>216683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230894</t>
+          <t>226575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30526</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14905</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>445564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>430569</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>452753</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>541</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>382965</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>376728</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>386795</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>468075</t>
+          <t>387655</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451611</t>
+          <t>381240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474928</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>851039</t>
+          <t>833218</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836323</t>
+          <t>817064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>859824</t>
+          <t>840871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
